--- a/artfynd/A 24696-2026 artfynd.xlsx
+++ b/artfynd/A 24696-2026 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>103711548</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596578.2488228416</v>
+        <v>596578</v>
       </c>
       <c r="R2" t="n">
-        <v>7072345.80647784</v>
+        <v>7072346</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +746,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 24696-2026 artfynd.xlsx
+++ b/artfynd/A 24696-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,332 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135274927</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>596677</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7072385</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135275217</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>596673</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7072364</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135275017</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>596592</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7072271</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24696-2026 artfynd.xlsx
+++ b/artfynd/A 24696-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1100,6 +1100,228 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135274794</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>596677</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7072385</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135275209</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>596673</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7072365</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24696-2026 artfynd.xlsx
+++ b/artfynd/A 24696-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103711548</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135274927</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135275217</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135275017</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135274794</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1321,8 +1351,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135275209</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 24696-2026 artfynd.xlsx
+++ b/artfynd/A 24696-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135274927</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>135275217</v>
       </c>
       <c r="B4" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>135275017</v>
       </c>
       <c r="B5" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>135274794</v>
       </c>
       <c r="B6" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>135275209</v>
       </c>
       <c r="B7" t="n">
-        <v>79131</v>
+        <v>79169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24696-2026 artfynd.xlsx
+++ b/artfynd/A 24696-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>135274927</v>
       </c>
       <c r="B3" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>135275217</v>
       </c>
       <c r="B4" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>135274794</v>
       </c>
       <c r="B6" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>135275209</v>
       </c>
       <c r="B7" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24696-2026 artfynd.xlsx
+++ b/artfynd/A 24696-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,9 +784,587 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135274927</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>596677</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7072385</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135274927</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135275217</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>596673</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7072364</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135275217</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135275017</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>596592</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7072271</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135275017</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135274794</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>596677</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7072385</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135274794</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135275209</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mehållstjärnarna, Mehållstjärnarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>596673</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7072365</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Johanna Liljegren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135275209</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
